--- a/lab4/доп.xlsx
+++ b/lab4/доп.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\Opd\lab4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\OPD\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F72321-0C40-4066-88E2-FC5A62DCD455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="163">
   <si>
     <t>Мнемоника</t>
   </si>
@@ -246,9 +245,6 @@
     <t>70</t>
   </si>
   <si>
-    <t>F3XX</t>
-  </si>
-  <si>
     <t>BNC</t>
   </si>
   <si>
@@ -511,12 +507,18 @@
   </si>
   <si>
     <t>NEG 02A (RES)</t>
+  </si>
+  <si>
+    <t>F305</t>
+  </si>
+  <si>
+    <t>0200</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -964,22 +966,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L79"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.453125" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" customWidth="1"/>
-    <col min="4" max="4" width="41.26953125" customWidth="1"/>
-    <col min="5" max="5" width="32.26953125" customWidth="1"/>
-    <col min="9" max="9" width="11.1796875" customWidth="1"/>
-    <col min="10" max="10" width="13.26953125" customWidth="1"/>
-    <col min="11" max="11" width="42.81640625" customWidth="1"/>
-    <col min="12" max="12" width="34.7265625" customWidth="1"/>
-    <col min="15" max="15" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="41.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="42.85546875" customWidth="1"/>
+    <col min="12" max="12" width="34.7109375" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -1005,7 +1007,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1019,7 +1021,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I2" s="4">
         <v>67</v>
@@ -1034,7 +1036,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1052,16 +1054,16 @@
         <v>70</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1087,10 +1089,10 @@
         <v>19</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1108,16 +1110,16 @@
         <v>71</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="L5" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1130,18 +1132,18 @@
         <v>49</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="5">
-        <v>100</v>
+      <c r="B7" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>1</v>
@@ -1159,21 +1161,21 @@
         <v>55</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
@@ -1186,13 +1188,13 @@
         <v>20</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>7</v>
       </c>
@@ -1207,7 +1209,7 @@
       </c>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>8</v>
       </c>
@@ -1215,7 +1217,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>52</v>
@@ -1227,30 +1229,30 @@
         <v>63</v>
       </c>
       <c r="J10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I11" s="7" t="s">
         <v>64</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -1258,13 +1260,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>65</v>
@@ -1276,37 +1278,37 @@
         <v>19</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E13" s="8"/>
       <c r="I13" s="7" t="s">
         <v>72</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="L13" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>3</v>
       </c>
@@ -1314,95 +1316,95 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" s="8"/>
       <c r="I14" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>49</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E15" s="8"/>
       <c r="I15" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>55</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" s="8"/>
       <c r="I16" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -1410,37 +1412,37 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E18" s="8"/>
       <c r="I18" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="J18" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="K18" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="L18" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="L18" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E19" s="8"/>
       <c r="I19" s="1"/>
@@ -1448,7 +1450,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>27</v>
       </c>
@@ -1456,10 +1458,10 @@
         <v>21</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E20" s="11"/>
       <c r="I20" s="1"/>
@@ -1467,7 +1469,7 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1480,18 +1482,18 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="E22" s="6"/>
       <c r="I22" s="1"/>
@@ -1499,7 +1501,7 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>34</v>
       </c>
@@ -1507,10 +1509,10 @@
         <v>31</v>
       </c>
       <c r="C23" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>125</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>126</v>
       </c>
       <c r="E23" s="11"/>
       <c r="I23" s="1"/>
@@ -1518,14 +1520,14 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>36</v>
       </c>
@@ -1533,16 +1535,16 @@
         <v>18</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>37</v>
       </c>
@@ -1550,14 +1552,14 @@
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E26" s="8"/>
     </row>
-    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>38</v>
       </c>
@@ -1565,15 +1567,15 @@
         <v>22</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>39</v>
       </c>
@@ -1581,16 +1583,16 @@
         <v>66</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>129</v>
-      </c>
       <c r="E29" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>40</v>
       </c>
@@ -1598,45 +1600,45 @@
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B32" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>35</v>
       </c>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>43</v>
       </c>
@@ -1644,16 +1646,16 @@
         <v>16</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>44</v>
       </c>
@@ -1661,14 +1663,14 @@
         <v>13</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E35" s="8"/>
     </row>
-    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>45</v>
       </c>
@@ -1676,20 +1678,20 @@
         <v>21</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>48</v>
       </c>
       <c r="E36" s="11"/>
     </row>
-    <row r="37" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>46</v>
       </c>
@@ -1697,27 +1699,27 @@
         <v>8004</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E39" s="11"/>
       <c r="G39" s="2"/>
@@ -1726,22 +1728,22 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>50</v>
@@ -1755,18 +1757,18 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="E42" s="8"/>
       <c r="G42" s="2"/>
@@ -1775,18 +1777,18 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E43" s="8"/>
       <c r="G43" s="3"/>
@@ -1795,18 +1797,18 @@
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E44" s="8"/>
       <c r="G44" s="2"/>
@@ -1815,15 +1817,15 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>35</v>
@@ -1835,9 +1837,9 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>11</v>
@@ -1846,7 +1848,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E46" s="11"/>
       <c r="G46" s="2"/>
@@ -1855,7 +1857,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1867,9 +1869,9 @@
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
     </row>
-    <row r="48" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>14</v>
@@ -1887,21 +1889,21 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1913,7 +1915,7 @@
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1925,7 +1927,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="G53" s="2"/>
@@ -1934,7 +1936,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1946,7 +1948,7 @@
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1958,7 +1960,7 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1970,7 +1972,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -1982,7 +1984,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1994,21 +1996,21 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2020,7 +2022,7 @@
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2032,7 +2034,7 @@
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2045,7 +2047,7 @@
       <c r="K63" s="3"/>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -2058,7 +2060,7 @@
       <c r="K64" s="3"/>
       <c r="L64" s="1"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2071,7 +2073,7 @@
       <c r="K65" s="3"/>
       <c r="L65" s="1"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2084,7 +2086,7 @@
       <c r="K66" s="2"/>
       <c r="L66" s="1"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2097,7 +2099,7 @@
       <c r="K67" s="2"/>
       <c r="L67" s="1"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -2110,7 +2112,7 @@
       <c r="K68" s="2"/>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2122,70 +2124,70 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
